--- a/Res.xlsx
+++ b/Res.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5897AC2C-B513-4FA9-ACCF-2A1C5967256B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,13 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
-  <si>
-    <t>Aditi</t>
-  </si>
-  <si>
-    <t>SRUTH</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>PALACHOLLA ANURADHA SRI TULASI MOUNIKA</t>
   </si>
@@ -106,12 +101,108 @@
   </si>
   <si>
     <t>M. SARAVANAPRIYA</t>
+  </si>
+  <si>
+    <t>https://github.com/NehalJain14/V2V-Automation-Testing</t>
+  </si>
+  <si>
+    <t>https://github.com/sakshi936/V-V_Testing_Material</t>
+  </si>
+  <si>
+    <t>https://github.com/NagaLakshmi15/V2V-Automation-Testing-Training</t>
+  </si>
+  <si>
+    <t>https://github.com/Abhinayatalla/V2V-Automation-Testing-Training-</t>
+  </si>
+  <si>
+    <t>https://github.com/Pooja-250/V2V-Automation-Testing-Training-</t>
+  </si>
+  <si>
+    <t>https://github.com/ShriyaDey/V2V_Automation_Testing_training</t>
+  </si>
+  <si>
+    <t>https://github.com/Simrandaultani/V2V-Automation-Testing-Training.git</t>
+  </si>
+  <si>
+    <t>https://github.com/2100032592cser-veena/V2V-Automation-Testing-Training</t>
+  </si>
+  <si>
+    <t>https://github.com/SIVAKUMARI2123/V2V-Automation-Testing-Training</t>
+  </si>
+  <si>
+    <t>https://github.com/palacholla-anuradha-sri-tulasi-mounika/V2V-Automation-Testing-Training-</t>
+  </si>
+  <si>
+    <t>https://github.com/karanamsirisha6/V2V-Automation-Testing-Training-</t>
+  </si>
+  <si>
+    <t>https://github.com/AishRRajput/V2V-Automation-Testing-Training-</t>
+  </si>
+  <si>
+    <t>https://github.com/swethasanaboyina12/V2V-Automation-Testing-Training</t>
+  </si>
+  <si>
+    <t>https://github.com/Varshini-29-hub-hub/V-V-Automation-Testing</t>
+  </si>
+  <si>
+    <t>https://github.com/sakshipersai/V-V-Automation-Testing</t>
+  </si>
+  <si>
+    <t>https://github.com/Ravuri-Lohitha/V2V-Automation-Testing-Training.git</t>
+  </si>
+  <si>
+    <t>https://github.com/AishwaryaTonni/Training</t>
+  </si>
+  <si>
+    <t>Shruti Nagendra Patil</t>
+  </si>
+  <si>
+    <t>https://github.com/Shrutipatil16/Training</t>
+  </si>
+  <si>
+    <t>https://github.com/puligillaakhila/V-V-Automation-Testing-</t>
+  </si>
+  <si>
+    <t>https://github.com/varsha99999</t>
+  </si>
+  <si>
+    <t>https://github.com/akankshya200321/VnV-Automation</t>
+  </si>
+  <si>
+    <t>Aditi yadav</t>
+  </si>
+  <si>
+    <t>https://github.com/aditi0423/registration-form</t>
+  </si>
+  <si>
+    <t>https://github.com/Kratika2610?tab=repositories</t>
+  </si>
+  <si>
+    <t>https://github.com/Neeti-Malviya-075/Capgemini_Training_Sessions</t>
+  </si>
+  <si>
+    <t>https://github.com/sonalikasamanta019-blip/V2V-Automation-Testing-Training-</t>
+  </si>
+  <si>
+    <t>https://github.com/harshitha080503/V2V-Automation-Testing-Training-</t>
+  </si>
+  <si>
+    <t>https://github.com/Dhiviani/-V2V_Automation-_Testing_Training-.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Sribabu9363/V2V_AUTOMATION_TESTING_TRAINING.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Saravanpriya/V2V-automation-testing-training-.git</t>
+  </si>
+  <si>
+    <t>https://github.com/HarikaSai-2707/V2V-Automation-Testing-Training</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -121,15 +212,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -137,12 +234,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -153,14 +278,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -198,7 +326,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -270,7 +398,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -443,162 +571,282 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="47.6640625" customWidth="1"/>
+    <col min="1" max="1" width="47.6328125" customWidth="1"/>
+    <col min="2" max="2" width="95.54296875" customWidth="1"/>
+    <col min="7" max="7" width="11.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="B16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B18" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B22" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="B23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="B24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="B25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="B26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="B27" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="B28" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="B29" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G29" s="1"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>29</v>
-      </c>
+      <c r="B30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -606,19 +854,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{e760c494-6550-44b4-8258-77c175d778b7}" enabled="1" method="Privileged" siteId="{76a2ae5a-9f00-4f6b-95ed-5d33d77c4d61}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>